--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486442_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486442_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7465</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3552</v>
+        <v>6.9535</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3913</v>
+        <v>-2.9535</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.1807</v>
+        <v>2.1038</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7479</v>
+        <v>-0.3983</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.4328</v>
+        <v>2.5022</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3734</v>
+        <v>6.847</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0674</v>
+        <v>1.7765</v>
       </c>
       <c r="L2" t="n">
-        <v>0.306</v>
+        <v>5.0705</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.5541</v>
+        <v>-4.7431</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8153</v>
+        <v>-2.1748</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.7388</v>
+        <v>-2.5683</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R2" t="n">
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>5.21</v>
+        <v>0.3794</v>
       </c>
       <c r="T2" t="n">
-        <v>3.8094</v>
+        <v>0.0216</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4006</v>
+        <v>0.3578</v>
       </c>
       <c r="V2" t="n">
-        <v>2.0647</v>
+        <v>1.9517</v>
       </c>
       <c r="W2" t="n">
         <v>2.2599</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1952</v>
+        <v>-0.3082</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9848</v>
+        <v>3.2198</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5621</v>
+        <v>3.6739</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5773</v>
+        <v>-0.454</v>
       </c>
       <c r="G3" t="n">
         <v>1.6263</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5977</v>
+        <v>0.8328</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6321</v>
+        <v>0.7439</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0344</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5443</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>G. KALSCHEUR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6598</v>
+        <v>3.0882</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7674</v>
+        <v>4.378</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.1076</v>
+        <v>-1.2898</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1038</v>
+        <v>-0.7887</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3983</v>
+        <v>-2.5059</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5022</v>
+        <v>1.7172</v>
       </c>
       <c r="J4" t="n">
-        <v>6.847</v>
+        <v>2.5305</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7765</v>
+        <v>-1.3925</v>
       </c>
       <c r="L4" t="n">
-        <v>5.0705</v>
+        <v>3.923</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.7431</v>
+        <v>-3.3191</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.1748</v>
+        <v>-1.1134</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.5683</v>
+        <v>-2.2057</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.435</v>
+        <v>1.9576</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9608</v>
+        <v>0.3374</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1644</v>
+        <v>0.1526</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2037</v>
+        <v>0.1847</v>
       </c>
       <c r="V4" t="n">
-        <v>1.9517</v>
+        <v>1.582</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2599</v>
+        <v>1.695</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3082</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.059</v>
+        <v>2.5172</v>
       </c>
       <c r="E5" t="n">
-        <v>4.885</v>
+        <v>2.8965</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8261</v>
+        <v>-0.3793</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0971</v>
+        <v>-2.1807</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3747</v>
+        <v>-0.7479</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.4719</v>
+        <v>-1.4328</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1504</v>
+        <v>0.3734</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8866</v>
+        <v>0.0674</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2638</v>
+        <v>0.306</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.2475</v>
+        <v>-2.5541</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5118</v>
+        <v>-0.8153</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.7357</v>
+        <v>-1.7388</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0516</v>
+        <v>1.9807</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6922</v>
+        <v>1.3507</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3594</v>
+        <v>0.63</v>
       </c>
       <c r="V5" t="n">
-        <v>1.017</v>
+        <v>2.0647</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>2.2599</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.113</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. KALSCHEUR</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8483</v>
+        <v>2.1583</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4155</v>
+        <v>4.9535</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5672</v>
+        <v>-2.7952</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7887</v>
+        <v>-1.0971</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.5059</v>
+        <v>1.3747</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7172</v>
+        <v>-2.4719</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5305</v>
+        <v>4.1504</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3925</v>
+        <v>2.8866</v>
       </c>
       <c r="L6" t="n">
-        <v>3.923</v>
+        <v>1.2638</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.3191</v>
+        <v>-5.2475</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1134</v>
+        <v>-1.5118</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.2057</v>
+        <v>-3.7357</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9026</v>
+        <v>1.1509</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8099</v>
+        <v>0.7607</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0927</v>
+        <v>0.3902</v>
       </c>
       <c r="V6" t="n">
-        <v>1.582</v>
+        <v>1.017</v>
       </c>
       <c r="W6" t="n">
-        <v>1.695</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
         <v>-0.113</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. IGLESIAS FERNANDEZ</t>
+          <t>K. SMITH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0786</v>
+        <v>0.8677</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7833</v>
+        <v>3.7021</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2953</v>
+        <v>-2.8344</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1538</v>
+        <v>0.9316</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0335</v>
+        <v>-1.1283</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1873</v>
+        <v>2.0599</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0382</v>
+        <v>3.2323</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.1341</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0382</v>
+        <v>3.0982</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1155</v>
+        <v>-2.3007</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0335</v>
+        <v>-1.2624</v>
       </c>
       <c r="O7" t="n">
-        <v>0.149</v>
+        <v>-1.0383</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9248</v>
+        <v>0.8911</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7451</v>
+        <v>0.4699</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1798</v>
+        <v>0.4212</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6499</v>
+        <v>0.6923</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8855</v>
+        <v>3.7737</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.2355</v>
+        <v>-3.0814</v>
       </c>
       <c r="G8" t="n">
         <v>1.1707</v>
@@ -1078,13 +1078,13 @@
         <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4368</v>
+        <v>0.4792</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4146</v>
+        <v>0.3028</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0222</v>
+        <v>0.1763</v>
       </c>
       <c r="V8" t="n">
         <v>0.5649999999999999</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. SMITH</t>
+          <t>M. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.323</v>
+        <v>0.62</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6963</v>
+        <v>0.448</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0194</v>
+        <v>0.172</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9316</v>
+        <v>0.1538</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1283</v>
+        <v>-0.0335</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0599</v>
+        <v>0.1873</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2323</v>
+        <v>0.0382</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1341</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3.0982</v>
+        <v>0.0382</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3007</v>
+        <v>0.1155</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2624</v>
+        <v>-0.0335</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0383</v>
+        <v>0.149</v>
       </c>
       <c r="P9" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2997</v>
+        <v>0.4663</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.536</v>
+        <v>0.4098</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2362</v>
+        <v>0.0565</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8</v>
+        <v>-1.8934</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4412</v>
+        <v>0.2862</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2412</v>
+        <v>-2.1796</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5434</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4437</v>
+        <v>0.3503</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2656</v>
+        <v>0.1106</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1781</v>
+        <v>0.2397</v>
       </c>
       <c r="V10" t="n">
         <v>-0.4828</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8856</v>
+        <v>-5.9096</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8974</v>
+        <v>-4.8289</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9882</v>
+        <v>-1.0807</v>
       </c>
       <c r="G11" t="n">
         <v>-6.3565</v>
@@ -1312,13 +1312,13 @@
         <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1986</v>
+        <v>-0.2226</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0649</v>
+        <v>0.0036</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1338</v>
+        <v>-0.2262</v>
       </c>
       <c r="V11" t="n">
         <v>0.452</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.0183</v>
+        <v>9.360499999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>25.8941</v>
+        <v>26.2365</v>
       </c>
       <c r="F12" t="n">
         <v>-16.8759</v>
@@ -1366,7 +1366,7 @@
         <v>22.0946</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2607</v>
+        <v>4.260699999999999</v>
       </c>
       <c r="L12" t="n">
         <v>17.8339</v>
@@ -1381,7 +1381,7 @@
         <v>-18.3559</v>
       </c>
       <c r="P12" t="n">
-        <v>4.350099999999999</v>
+        <v>4.3501</v>
       </c>
       <c r="Q12" t="n">
         <v>-8.700200000000001</v>
@@ -1390,16 +1390,16 @@
         <v>13.0504</v>
       </c>
       <c r="S12" t="n">
-        <v>6.302899999999999</v>
+        <v>6.645499999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>3.9838</v>
+        <v>4.326199999999999</v>
       </c>
       <c r="U12" t="n">
         <v>2.3191</v>
       </c>
       <c r="V12" t="n">
-        <v>4.345400000000001</v>
+        <v>4.3454</v>
       </c>
       <c r="W12" t="n">
         <v>8.5161</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.1091</v>
+        <v>4.4766</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5811</v>
+        <v>5.8047</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.472</v>
+        <v>-1.3281</v>
       </c>
       <c r="G13" t="n">
         <v>5.135</v>
@@ -1468,13 +1468,13 @@
         <v>1.0875</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3309</v>
+        <v>-0.9635</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0274</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3034</v>
+        <v>-0.1595</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5649999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7965</v>
+        <v>1.6424</v>
       </c>
       <c r="E14" t="n">
         <v>1.0167</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7798</v>
+        <v>0.6257</v>
       </c>
       <c r="G14" t="n">
         <v>1.7178</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2962</v>
+        <v>0.1421</v>
       </c>
       <c r="T14" t="n">
         <v>0.012</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2842</v>
+        <v>0.1301</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9213</v>
+        <v>1.3619</v>
       </c>
       <c r="E15" t="n">
-        <v>3.89</v>
+        <v>4.0017</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.9686</v>
+        <v>-2.6398</v>
       </c>
       <c r="G15" t="n">
         <v>2.207</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.4329</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3509</v>
+        <v>-0.2391</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5226</v>
+        <v>-0.1938</v>
       </c>
       <c r="V15" t="n">
         <v>-1.4997</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VAULET</t>
+          <t>S. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1271</v>
+        <v>1.1748</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5355</v>
+        <v>4.8943</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4084</v>
+        <v>-3.7195</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1545</v>
+        <v>2.683</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3498</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1952</v>
+        <v>2.1603</v>
       </c>
       <c r="J16" t="n">
-        <v>0.604</v>
+        <v>6.101</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5657</v>
+        <v>1.6059</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0382</v>
+        <v>4.4951</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4495</v>
+        <v>-3.418</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.216</v>
+        <v>-1.0832</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2335</v>
+        <v>-2.3348</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0274</v>
+        <v>-0.9857</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.3569</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0411</v>
+        <v>-0.6288</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. GARCIA CALVO</t>
+          <t>J. VAULET</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0521</v>
+        <v>0.1888</v>
       </c>
       <c r="E17" t="n">
-        <v>4.2237</v>
+        <v>0.5355</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.1716</v>
+        <v>-0.3467</v>
       </c>
       <c r="G17" t="n">
-        <v>2.683</v>
+        <v>0.1545</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.3498</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1603</v>
+        <v>-0.1952</v>
       </c>
       <c r="J17" t="n">
-        <v>6.101</v>
+        <v>0.604</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6059</v>
+        <v>0.5657</v>
       </c>
       <c r="L17" t="n">
-        <v>4.4951</v>
+        <v>0.0382</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.418</v>
+        <v>-0.4495</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0832</v>
+        <v>-0.216</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.3348</v>
+        <v>-0.2335</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.1084</v>
+        <v>0.0342</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0274</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0809</v>
+        <v>0.1027</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1647</v>
+        <v>-1.0529</v>
       </c>
       <c r="E18" t="n">
-        <v>0.648</v>
+        <v>0.7598</v>
       </c>
       <c r="F18" t="n">
         <v>-1.8127</v>
@@ -1858,10 +1858,10 @@
         <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1406</v>
+        <v>0.2524</v>
       </c>
       <c r="U18" t="n">
         <v>-0.2091</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>O. SILVERIO GRULLON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5603</v>
+        <v>-1.6077</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6173</v>
+        <v>3.8617</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.1776</v>
+        <v>-5.4695</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5868</v>
+        <v>1.3055</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4986</v>
+        <v>3.3853</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0854</v>
+        <v>-2.0798</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7984</v>
+        <v>5.306</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5689</v>
+        <v>4.137</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2295</v>
+        <v>1.169</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3852</v>
+        <v>-4.0005</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0703</v>
+        <v>-0.7517</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.3149</v>
+        <v>-3.2488</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2175</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.305</v>
+        <v>-3.2626</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8737</v>
+        <v>-1.5859</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4937</v>
+        <v>-0.6369</v>
       </c>
       <c r="U19" t="n">
-        <v>0.38</v>
+        <v>-0.9491000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.6297</v>
+        <v>0.1952</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3698</v>
+        <v>2.4552</v>
       </c>
       <c r="X19" t="n">
         <v>-2.2599</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. SILVERIO GRULLON</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8151</v>
+        <v>-3.8033</v>
       </c>
       <c r="E20" t="n">
-        <v>3.4147</v>
+        <v>-0.379</v>
       </c>
       <c r="F20" t="n">
-        <v>-6.2298</v>
+        <v>-3.4244</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3055</v>
+        <v>-2.6437</v>
       </c>
       <c r="H20" t="n">
-        <v>3.3853</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0798</v>
+        <v>-2.0535</v>
       </c>
       <c r="J20" t="n">
-        <v>5.306</v>
+        <v>1.3695</v>
       </c>
       <c r="K20" t="n">
-        <v>4.137</v>
+        <v>0.2587</v>
       </c>
       <c r="L20" t="n">
-        <v>1.169</v>
+        <v>1.1108</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.0005</v>
+        <v>-4.0132</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7517</v>
+        <v>-0.8488</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.2488</v>
+        <v>-3.1643</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5225</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.2626</v>
+        <v>-1.305</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.7933</v>
+        <v>-1.1167</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0839</v>
+        <v>-0.4434</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.7094</v>
+        <v>-0.6733</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1952</v>
+        <v>0.1745</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.2599</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4385</v>
+        <v>-3.9245</v>
       </c>
       <c r="E21" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.5003</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5066</v>
+        <v>-3.4242</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6437</v>
+        <v>-1.5868</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5901999999999999</v>
+        <v>0.4986</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0535</v>
+        <v>-2.0854</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3695</v>
+        <v>0.7984</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2587</v>
+        <v>0.5689</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1108</v>
+        <v>0.2295</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.0132</v>
+        <v>-2.3852</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8488</v>
+        <v>-0.0703</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.1643</v>
+        <v>-2.3149</v>
       </c>
       <c r="P21" t="n">
         <v>-0.2175</v>
@@ -2092,22 +2092,22 @@
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7519</v>
+        <v>0.5095</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0036</v>
+        <v>0.3761</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7554999999999999</v>
+        <v>0.1334</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1745</v>
+        <v>-2.6297</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X21" t="n">
-        <v>0.1745</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.0457</v>
+        <v>-5.9841</v>
       </c>
       <c r="E22" t="n">
         <v>-3.1192</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9265</v>
+        <v>-2.8649</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7215</v>
@@ -2170,13 +2170,13 @@
         <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5189</v>
+        <v>-0.4572</v>
       </c>
       <c r="T22" t="n">
         <v>-0.411</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1079</v>
+        <v>-0.0463</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1952</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.0182</v>
+        <v>-7.527999999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>16.8759</v>
+        <v>16.87590000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-25.894</v>
+        <v>-24.4041</v>
       </c>
       <c r="G23" t="n">
         <v>5.980099999999999</v>
@@ -2218,22 +2218,22 @@
         <v>5.4583</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5219999999999998</v>
+        <v>0.5220000000000002</v>
       </c>
       <c r="J23" t="n">
         <v>28.0747</v>
       </c>
       <c r="K23" t="n">
-        <v>9.718799999999998</v>
+        <v>9.7188</v>
       </c>
       <c r="L23" t="n">
-        <v>18.3557</v>
+        <v>18.35570000000001</v>
       </c>
       <c r="M23" t="n">
         <v>-22.0946</v>
       </c>
       <c r="N23" t="n">
-        <v>-4.2607</v>
+        <v>-4.260699999999999</v>
       </c>
       <c r="O23" t="n">
         <v>-17.8338</v>
@@ -2248,13 +2248,13 @@
         <v>8.700099999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.3029</v>
+        <v>-4.8128</v>
       </c>
       <c r="T23" t="n">
         <v>-2.3192</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.9835</v>
+        <v>-2.4937</v>
       </c>
       <c r="V23" t="n">
         <v>-4.3453</v>
